--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356400</v>
+        <v>113356530</v>
       </c>
       <c r="B2" t="n">
-        <v>96261</v>
+        <v>79210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747858</v>
+        <v>748040</v>
       </c>
       <c r="R2" t="n">
-        <v>7201448</v>
+        <v>7201676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B3" t="n">
-        <v>79194</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R3" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356399</v>
+        <v>113356531</v>
       </c>
       <c r="B4" t="n">
-        <v>96261</v>
+        <v>79210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747743</v>
+        <v>748077</v>
       </c>
       <c r="R4" t="n">
-        <v>7201632</v>
+        <v>7201765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356530</v>
+        <v>113356400</v>
       </c>
       <c r="B5" t="n">
-        <v>79194</v>
+        <v>96277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748040</v>
+        <v>747858</v>
       </c>
       <c r="R5" t="n">
-        <v>7201676</v>
+        <v>7201448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356530</v>
+        <v>113356531</v>
       </c>
       <c r="B2" t="n">
         <v>79210</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748040</v>
+        <v>748077</v>
       </c>
       <c r="R2" t="n">
-        <v>7201676</v>
+        <v>7201765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356531</v>
+        <v>113356530</v>
       </c>
       <c r="B4" t="n">
         <v>79210</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748077</v>
+        <v>748040</v>
       </c>
       <c r="R4" t="n">
-        <v>7201765</v>
+        <v>7201676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356531</v>
       </c>
       <c r="B2" t="n">
-        <v>79210</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113356399</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356530</v>
+        <v>113356400</v>
       </c>
       <c r="B4" t="n">
-        <v>79210</v>
+        <v>96289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748040</v>
+        <v>747858</v>
       </c>
       <c r="R4" t="n">
-        <v>7201676</v>
+        <v>7201448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356400</v>
+        <v>113356530</v>
       </c>
       <c r="B5" t="n">
-        <v>96277</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747858</v>
+        <v>748040</v>
       </c>
       <c r="R5" t="n">
-        <v>7201448</v>
+        <v>7201676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356399</v>
+        <v>113356400</v>
       </c>
       <c r="B3" t="n">
         <v>96289</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747743</v>
+        <v>747858</v>
       </c>
       <c r="R3" t="n">
-        <v>7201632</v>
+        <v>7201448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356400</v>
+        <v>113356530</v>
       </c>
       <c r="B4" t="n">
-        <v>96289</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747858</v>
+        <v>748040</v>
       </c>
       <c r="R4" t="n">
-        <v>7201448</v>
+        <v>7201676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356530</v>
+        <v>113356399</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>96289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748040</v>
+        <v>747743</v>
       </c>
       <c r="R5" t="n">
-        <v>7201676</v>
+        <v>7201632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356531</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>79244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356400</v>
+        <v>113356399</v>
       </c>
       <c r="B3" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747858</v>
+        <v>747743</v>
       </c>
       <c r="R3" t="n">
-        <v>7201448</v>
+        <v>7201632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356530</v>
+        <v>113356400</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>96311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748040</v>
+        <v>747858</v>
       </c>
       <c r="R4" t="n">
-        <v>7201676</v>
+        <v>7201448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356399</v>
+        <v>113356530</v>
       </c>
       <c r="B5" t="n">
-        <v>96289</v>
+        <v>79244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747743</v>
+        <v>748040</v>
       </c>
       <c r="R5" t="n">
-        <v>7201632</v>
+        <v>7201676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356531</v>
+        <v>113356530</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79248</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748077</v>
+        <v>748040</v>
       </c>
       <c r="R2" t="n">
-        <v>7201765</v>
+        <v>7201676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356399</v>
+        <v>113356400</v>
       </c>
       <c r="B3" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747743</v>
+        <v>747858</v>
       </c>
       <c r="R3" t="n">
-        <v>7201632</v>
+        <v>7201448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356400</v>
+        <v>113356399</v>
       </c>
       <c r="B4" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747858</v>
+        <v>747743</v>
       </c>
       <c r="R4" t="n">
-        <v>7201448</v>
+        <v>7201632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356530</v>
+        <v>113356531</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79248</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748040</v>
+        <v>748077</v>
       </c>
       <c r="R5" t="n">
-        <v>7201676</v>
+        <v>7201765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356530</v>
+        <v>113356531</v>
       </c>
       <c r="B2" t="n">
         <v>79248</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748040</v>
+        <v>748077</v>
       </c>
       <c r="R2" t="n">
-        <v>7201676</v>
+        <v>7201765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356399</v>
+        <v>113356530</v>
       </c>
       <c r="B4" t="n">
-        <v>96315</v>
+        <v>79248</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747743</v>
+        <v>748040</v>
       </c>
       <c r="R4" t="n">
-        <v>7201632</v>
+        <v>7201676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R5" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356531</v>
+        <v>113356400</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>96321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748077</v>
+        <v>747858</v>
       </c>
       <c r="R2" t="n">
-        <v>7201765</v>
+        <v>7201448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356400</v>
+        <v>113356399</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747858</v>
+        <v>747743</v>
       </c>
       <c r="R3" t="n">
-        <v>7201448</v>
+        <v>7201632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>113356530</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356399</v>
+        <v>113356531</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>79254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747743</v>
+        <v>748077</v>
       </c>
       <c r="R5" t="n">
-        <v>7201632</v>
+        <v>7201765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356400</v>
+        <v>113356531</v>
       </c>
       <c r="B2" t="n">
-        <v>96321</v>
+        <v>79254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747858</v>
+        <v>748077</v>
       </c>
       <c r="R2" t="n">
-        <v>7201448</v>
+        <v>7201765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356399</v>
+        <v>113356530</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>79254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747743</v>
+        <v>748040</v>
       </c>
       <c r="R3" t="n">
-        <v>7201632</v>
+        <v>7201676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356530</v>
+        <v>113356399</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748040</v>
+        <v>747743</v>
       </c>
       <c r="R4" t="n">
-        <v>7201676</v>
+        <v>7201632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356531</v>
+        <v>113356400</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>96321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748077</v>
+        <v>747858</v>
       </c>
       <c r="R5" t="n">
-        <v>7201765</v>
+        <v>7201448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>96328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R2" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
         <v>113356530</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356399</v>
+        <v>113356400</v>
       </c>
       <c r="B4" t="n">
-        <v>96321</v>
+        <v>96328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747743</v>
+        <v>747858</v>
       </c>
       <c r="R4" t="n">
-        <v>7201632</v>
+        <v>7201448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356400</v>
+        <v>113356531</v>
       </c>
       <c r="B5" t="n">
-        <v>96321</v>
+        <v>79261</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747858</v>
+        <v>748077</v>
       </c>
       <c r="R5" t="n">
-        <v>7201448</v>
+        <v>7201765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356399</v>
+        <v>113356400</v>
       </c>
       <c r="B2" t="n">
-        <v>96328</v>
+        <v>96333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747743</v>
+        <v>747858</v>
       </c>
       <c r="R2" t="n">
-        <v>7201632</v>
+        <v>7201448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>113356530</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356400</v>
+        <v>113356531</v>
       </c>
       <c r="B4" t="n">
-        <v>96328</v>
+        <v>79263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747858</v>
+        <v>748077</v>
       </c>
       <c r="R4" t="n">
-        <v>7201448</v>
+        <v>7201765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>96333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R5" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356400</v>
       </c>
       <c r="B2" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356530</v>
+        <v>113356531</v>
       </c>
       <c r="B3" t="n">
-        <v>79263</v>
+        <v>79291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748040</v>
+        <v>748077</v>
       </c>
       <c r="R3" t="n">
-        <v>7201676</v>
+        <v>7201765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B4" t="n">
-        <v>79263</v>
+        <v>96361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R4" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356399</v>
+        <v>113356530</v>
       </c>
       <c r="B5" t="n">
-        <v>96333</v>
+        <v>79291</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747743</v>
+        <v>748040</v>
       </c>
       <c r="R5" t="n">
-        <v>7201632</v>
+        <v>7201676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356400</v>
+        <v>113356530</v>
       </c>
       <c r="B2" t="n">
-        <v>96361</v>
+        <v>79291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747858</v>
+        <v>748040</v>
       </c>
       <c r="R2" t="n">
-        <v>7201448</v>
+        <v>7201676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356531</v>
+        <v>113356399</v>
       </c>
       <c r="B3" t="n">
-        <v>79291</v>
+        <v>96361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748077</v>
+        <v>747743</v>
       </c>
       <c r="R3" t="n">
-        <v>7201765</v>
+        <v>7201632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356399</v>
+        <v>113356400</v>
       </c>
       <c r="B4" t="n">
         <v>96361</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747743</v>
+        <v>747858</v>
       </c>
       <c r="R4" t="n">
-        <v>7201632</v>
+        <v>7201448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356530</v>
+        <v>113356531</v>
       </c>
       <c r="B5" t="n">
         <v>79291</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748040</v>
+        <v>748077</v>
       </c>
       <c r="R5" t="n">
-        <v>7201676</v>
+        <v>7201765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356400</v>
+        <v>113356530</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747858</v>
+        <v>748040</v>
       </c>
       <c r="R2" t="n">
-        <v>7201449</v>
+        <v>7201676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356399</v>
+        <v>113356531</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747743</v>
+        <v>748077</v>
       </c>
       <c r="R3" t="n">
-        <v>7201632</v>
+        <v>7201765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356530</v>
+        <v>113356399</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748040</v>
+        <v>747743</v>
       </c>
       <c r="R4" t="n">
-        <v>7201676</v>
+        <v>7201632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356531</v>
+        <v>113356400</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748077</v>
+        <v>747858</v>
       </c>
       <c r="R5" t="n">
-        <v>7201765</v>
+        <v>7201449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11627-2023 artfynd.xlsx
+++ b/artfynd/A 11627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356530</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356531</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356400</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>